--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260605_211819.xlsx
@@ -5864,7 +5864,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
